--- a/data/raw/_synthetic/headcount_by_department.xlsx
+++ b/data/raw/_synthetic/headcount_by_department.xlsx
@@ -540,7 +540,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>63500</v>
+        <v>62500</v>
       </c>
     </row>
     <row r="10">
@@ -553,7 +553,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>29000</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="11">
@@ -566,7 +566,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>33500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="12">
@@ -579,7 +579,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>22000</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="13">
@@ -592,7 +592,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>11500</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="14">
@@ -605,7 +605,7 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>10500</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
